--- a/Campaign-Creation-Without-Live-Pavani_Final-Worksheet.xlsx
+++ b/Campaign-Creation-Without-Live-Pavani_Final-Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavani\Desktop\Pavani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590A3980-19E7-470B-8D0F-2370857BCAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8772ECF8-DBCE-4C3B-BF39-439F7444B973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{1C483EA2-1013-4C19-9A4E-B7ECB3E0844B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1C483EA2-1013-4C19-9A4E-B7ECB3E0844B}"/>
   </bookViews>
   <sheets>
     <sheet name="Campaign Objectives" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="107">
   <si>
     <t>I am practicing the adwords without Live campaigns</t>
   </si>
@@ -325,9 +325,6 @@
   </si>
   <si>
     <t>Description:</t>
-  </si>
-  <si>
-    <t>Understand search intent &amp; improve rankings. Simple guide for beginners. Start learning now.</t>
   </si>
   <si>
     <t>🔹 Ad Version 2</t>
@@ -651,13 +648,34 @@
   </si>
   <si>
     <t>🧠 2. Campaign Strategy</t>
+  </si>
+  <si>
+    <t>Understand search intent &amp; improve rankings. Simple guide for beginners. Learn now.</t>
+  </si>
+  <si>
+    <t>Created Ad</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Disclaimer: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Above screenshots are estimated based on given details</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -750,6 +768,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -778,7 +811,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -798,6 +831,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -814,6 +848,227 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>590660</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>89099</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F656598-B0BE-2181-4DE1-EEDE34A13E61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3835400" y="774700"/>
+          <a:ext cx="2140060" cy="3873699"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>247788</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>69983</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB930B7F-F48D-1B36-CA16-7B5F7AAF6335}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7213600" y="762000"/>
+          <a:ext cx="2686188" cy="2578233"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>273189</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>38178</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B66166A-AA15-D910-1228-154A47F8EEC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7213600" y="3822700"/>
+          <a:ext cx="2711589" cy="1511378"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>400396</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>177934</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5532E6E4-23ED-F945-D70C-1043CA894DBD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="273050" y="4889500"/>
+          <a:ext cx="6731346" cy="2609984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1160,7 +1415,7 @@
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B7" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.35">
@@ -1175,17 +1430,17 @@
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B10" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.35">
@@ -1195,7 +1450,7 @@
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1271,19 +1526,19 @@
   <sheetData>
     <row r="5" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B5" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>53</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -1313,7 +1568,7 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="C9" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>39</v>
@@ -1385,7 +1640,7 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>36</v>
@@ -1399,7 +1654,7 @@
         <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
@@ -1415,18 +1670,18 @@
         <v>30</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="C19" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>47</v>
@@ -1444,7 +1699,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="F22" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.35">
@@ -1452,7 +1707,7 @@
         <v>49</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.35">
@@ -1475,12 +1730,12 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="F27" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
@@ -1490,12 +1745,12 @@
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F33" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F34" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="6:6" x14ac:dyDescent="0.35">
@@ -1505,7 +1760,7 @@
     </row>
     <row r="38" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F38" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1515,7 +1770,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5245F617-7270-4B06-B0F0-702522BD912E}">
-  <dimension ref="A2:B36"/>
+  <dimension ref="A2:J42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.1796875" style="1" customWidth="1"/>
@@ -1523,56 +1778,65 @@
     <col min="3" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="31" x14ac:dyDescent="0.7">
+    <row r="2" spans="2:10" ht="31" x14ac:dyDescent="0.7">
       <c r="B2" s="12" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="16" x14ac:dyDescent="0.4">
+      <c r="B6" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="16" x14ac:dyDescent="0.4">
+      <c r="B7" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="16" x14ac:dyDescent="0.4">
+      <c r="B8" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B10" s="11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="16" x14ac:dyDescent="0.4">
-      <c r="B6" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" ht="16" x14ac:dyDescent="0.4">
-      <c r="B7" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" ht="16" x14ac:dyDescent="0.4">
-      <c r="B8" s="5" t="s">
+    <row r="12" spans="2:10" ht="16" x14ac:dyDescent="0.4">
+      <c r="B12" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B10" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" ht="16" x14ac:dyDescent="0.4">
-      <c r="B12" s="5" t="s">
+    <row r="13" spans="2:10" ht="16" x14ac:dyDescent="0.4">
+      <c r="B13" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="16" x14ac:dyDescent="0.4">
-      <c r="B13" s="5" t="s">
+    <row r="14" spans="2:10" ht="16" x14ac:dyDescent="0.4">
+      <c r="B14" s="5" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" ht="16" x14ac:dyDescent="0.4">
-      <c r="B14" s="5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="9"/>
     </row>
+    <row r="42" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A42" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1661,12 +1925,12 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B13" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B16" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
@@ -1674,32 +1938,32 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B18" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B22" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B23" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.4">
@@ -1707,7 +1971,7 @@
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
